--- a/_backup/tp_crown_jewel_os_mapped.xlsx
+++ b/_backup/tp_crown_jewel_os_mapped.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jibin.george\Documents\CD-TP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jibin.george\Documents\CD-TP\OS-Health-Check\_backup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A233AD89-D6CA-4D59-BA38-F47D521055A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC8A8709-D68F-4752-BBF3-A2F3F0845C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{37FBBB10-619C-4389-8764-5AE2A9612F89}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="282">
   <si>
     <t>os_string</t>
   </si>
@@ -134,9 +134,6 @@
     <t>Cisco IOS 12.1</t>
   </si>
   <si>
-    <t>Cisco IOS 12</t>
-  </si>
-  <si>
     <t>Cisco IOS 12.1(22)EA13</t>
   </si>
   <si>
@@ -588,9 +585,6 @@
   </si>
   <si>
     <t>Cisco PIX 8.2</t>
-  </si>
-  <si>
-    <t>Cisco PIX / Palo Alto Firewall</t>
   </si>
   <si>
     <t>Fortinet FortiGate 7.4.11</t>
@@ -1264,6 +1258,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D14E3EF5-7182-4FD0-AE49-F60BC3030398}">
   <dimension ref="A1:G175"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="38.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="75.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -1478,18 +1480,24 @@
         <v>30</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
+        <v>30</v>
+      </c>
+      <c r="D18">
+        <v>1173916800</v>
+      </c>
+      <c r="F18">
+        <v>1331769600</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C19" t="s">
         <v>30</v>
@@ -1503,10 +1511,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C20" t="s">
         <v>30</v>
@@ -1520,10 +1528,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C21" t="s">
         <v>30</v>
@@ -1537,13 +1545,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" t="s">
         <v>35</v>
-      </c>
-      <c r="B22" t="s">
-        <v>35</v>
-      </c>
-      <c r="C22" t="s">
-        <v>36</v>
       </c>
       <c r="D22">
         <v>1344816000</v>
@@ -1554,13 +1562,13 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D23">
         <v>1344816000</v>
@@ -1571,13 +1579,13 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D24">
         <v>1344816000</v>
@@ -1588,13 +1596,13 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D25">
         <v>1344816000</v>
@@ -1605,13 +1613,13 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D26">
         <v>1344816000</v>
@@ -1622,13 +1630,13 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D27">
         <v>1344816000</v>
@@ -1639,13 +1647,13 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C28" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D28">
         <v>1344816000</v>
@@ -1656,13 +1664,13 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D29">
         <v>1344816000</v>
@@ -1673,13 +1681,13 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D30">
         <v>1344816000</v>
@@ -1690,13 +1698,13 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D31">
         <v>1344816000</v>
@@ -1707,13 +1715,13 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D32">
         <v>1344816000</v>
@@ -1724,13 +1732,13 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B33" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D33">
         <v>1344816000</v>
@@ -1741,13 +1749,13 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C34" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D34">
         <v>1344816000</v>
@@ -1758,13 +1766,13 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D35">
         <v>1344816000</v>
@@ -1775,13 +1783,13 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D36">
         <v>1344816000</v>
@@ -1792,24 +1800,30 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B37" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C37" t="s">
-        <v>31</v>
+        <v>50</v>
+      </c>
+      <c r="D37">
+        <v>1454198400</v>
+      </c>
+      <c r="F37">
+        <v>1454198400</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
+        <v>51</v>
+      </c>
+      <c r="B38" t="s">
         <v>52</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>53</v>
-      </c>
-      <c r="C38" t="s">
-        <v>54</v>
       </c>
       <c r="D38">
         <v>1463961600</v>
@@ -1820,13 +1834,13 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
+        <v>52</v>
+      </c>
+      <c r="B39" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" t="s">
         <v>53</v>
-      </c>
-      <c r="B39" t="s">
-        <v>55</v>
-      </c>
-      <c r="C39" t="s">
-        <v>54</v>
       </c>
       <c r="D39">
         <v>1463961600</v>
@@ -1837,13 +1851,13 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
+        <v>54</v>
+      </c>
+      <c r="B40" t="s">
         <v>55</v>
       </c>
-      <c r="B40" t="s">
-        <v>56</v>
-      </c>
       <c r="C40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D40">
         <v>1463961600</v>
@@ -1854,13 +1868,13 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
+        <v>55</v>
+      </c>
+      <c r="B41" t="s">
         <v>56</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>57</v>
-      </c>
-      <c r="C41" t="s">
-        <v>58</v>
       </c>
       <c r="D41">
         <v>1597363200</v>
@@ -1871,13 +1885,13 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
+        <v>56</v>
+      </c>
+      <c r="B42" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42" t="s">
         <v>57</v>
-      </c>
-      <c r="B42" t="s">
-        <v>59</v>
-      </c>
-      <c r="C42" t="s">
-        <v>58</v>
       </c>
       <c r="D42">
         <v>1597363200</v>
@@ -1888,13 +1902,13 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
+        <v>58</v>
+      </c>
+      <c r="B43" t="s">
         <v>59</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>60</v>
-      </c>
-      <c r="C43" t="s">
-        <v>61</v>
       </c>
       <c r="D43">
         <v>1597363200</v>
@@ -1905,13 +1919,13 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
+        <v>59</v>
+      </c>
+      <c r="B44" t="s">
+        <v>61</v>
+      </c>
+      <c r="C44" t="s">
         <v>60</v>
-      </c>
-      <c r="B44" t="s">
-        <v>62</v>
-      </c>
-      <c r="C44" t="s">
-        <v>61</v>
       </c>
       <c r="D44">
         <v>1597363200</v>
@@ -1922,13 +1936,13 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45" t="s">
         <v>62</v>
       </c>
-      <c r="B45" t="s">
-        <v>63</v>
-      </c>
       <c r="C45" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D45">
         <v>1597363200</v>
@@ -1939,13 +1953,13 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
+        <v>62</v>
+      </c>
+      <c r="B46" t="s">
         <v>63</v>
       </c>
-      <c r="B46" t="s">
-        <v>64</v>
-      </c>
       <c r="C46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D46">
         <v>1597363200</v>
@@ -1956,13 +1970,13 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
+        <v>63</v>
+      </c>
+      <c r="B47" t="s">
         <v>64</v>
       </c>
-      <c r="B47" t="s">
-        <v>65</v>
-      </c>
       <c r="C47" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D47">
         <v>1597363200</v>
@@ -1973,13 +1987,13 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
+        <v>64</v>
+      </c>
+      <c r="B48" t="s">
         <v>65</v>
       </c>
-      <c r="B48" t="s">
-        <v>66</v>
-      </c>
       <c r="C48" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D48">
         <v>1597363200</v>
@@ -1990,13 +2004,13 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
+        <v>65</v>
+      </c>
+      <c r="B49" t="s">
         <v>66</v>
       </c>
-      <c r="B49" t="s">
-        <v>67</v>
-      </c>
       <c r="C49" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D49">
         <v>1597363200</v>
@@ -2007,13 +2021,13 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
+        <v>66</v>
+      </c>
+      <c r="B50" t="s">
         <v>67</v>
       </c>
-      <c r="B50" t="s">
-        <v>68</v>
-      </c>
       <c r="C50" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D50">
         <v>1597363200</v>
@@ -2024,13 +2038,13 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
+        <v>67</v>
+      </c>
+      <c r="B51" t="s">
         <v>68</v>
       </c>
-      <c r="B51" t="s">
-        <v>69</v>
-      </c>
       <c r="C51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D51">
         <v>1597363200</v>
@@ -2041,13 +2055,13 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
+        <v>68</v>
+      </c>
+      <c r="B52" t="s">
         <v>69</v>
       </c>
-      <c r="B52" t="s">
-        <v>70</v>
-      </c>
       <c r="C52" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D52">
         <v>1597363200</v>
@@ -2058,13 +2072,13 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
+        <v>69</v>
+      </c>
+      <c r="B53" t="s">
         <v>70</v>
       </c>
-      <c r="B53" t="s">
-        <v>71</v>
-      </c>
       <c r="C53" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D53">
         <v>1597363200</v>
@@ -2075,13 +2089,13 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
+        <v>70</v>
+      </c>
+      <c r="B54" t="s">
         <v>71</v>
       </c>
-      <c r="B54" t="s">
-        <v>72</v>
-      </c>
       <c r="C54" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D54">
         <v>1597363200</v>
@@ -2092,13 +2106,13 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
+        <v>71</v>
+      </c>
+      <c r="B55" t="s">
         <v>72</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
         <v>73</v>
-      </c>
-      <c r="C55" t="s">
-        <v>74</v>
       </c>
       <c r="D55">
         <v>1488326400</v>
@@ -2109,13 +2123,13 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
+        <v>74</v>
+      </c>
+      <c r="B56" t="s">
+        <v>74</v>
+      </c>
+      <c r="C56" t="s">
         <v>75</v>
-      </c>
-      <c r="B56" t="s">
-        <v>75</v>
-      </c>
-      <c r="C56" t="s">
-        <v>76</v>
       </c>
       <c r="D56">
         <v>1559692800</v>
@@ -2126,13 +2140,13 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
+        <v>76</v>
+      </c>
+      <c r="B57" t="s">
+        <v>76</v>
+      </c>
+      <c r="C57" t="s">
         <v>77</v>
-      </c>
-      <c r="B57" t="s">
-        <v>77</v>
-      </c>
-      <c r="C57" t="s">
-        <v>78</v>
       </c>
       <c r="D57">
         <v>1604966400</v>
@@ -2143,13 +2157,13 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B58" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C58" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D58">
         <v>1604966400</v>
@@ -2160,13 +2174,13 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
+        <v>79</v>
+      </c>
+      <c r="B59" t="s">
         <v>80</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C59" t="s">
         <v>81</v>
-      </c>
-      <c r="C59" t="s">
-        <v>82</v>
       </c>
       <c r="D59">
         <v>1690761600</v>
@@ -2177,13 +2191,13 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B60" t="s">
+        <v>80</v>
+      </c>
+      <c r="C60" t="s">
         <v>81</v>
-      </c>
-      <c r="C60" t="s">
-        <v>82</v>
       </c>
       <c r="D60">
         <v>1690761600</v>
@@ -2194,13 +2208,13 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B61" t="s">
+        <v>80</v>
+      </c>
+      <c r="C61" t="s">
         <v>81</v>
-      </c>
-      <c r="C61" t="s">
-        <v>82</v>
       </c>
       <c r="D61">
         <v>1690761600</v>
@@ -2211,13 +2225,13 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B62" t="s">
+        <v>80</v>
+      </c>
+      <c r="C62" t="s">
         <v>81</v>
-      </c>
-      <c r="C62" t="s">
-        <v>82</v>
       </c>
       <c r="D62">
         <v>1690761600</v>
@@ -2228,13 +2242,13 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B63" t="s">
+        <v>80</v>
+      </c>
+      <c r="C63" t="s">
         <v>81</v>
-      </c>
-      <c r="C63" t="s">
-        <v>82</v>
       </c>
       <c r="D63">
         <v>1690761600</v>
@@ -2245,13 +2259,13 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B64" t="s">
+        <v>80</v>
+      </c>
+      <c r="C64" t="s">
         <v>81</v>
-      </c>
-      <c r="C64" t="s">
-        <v>82</v>
       </c>
       <c r="D64">
         <v>1690761600</v>
@@ -2262,13 +2276,13 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B65" t="s">
+        <v>80</v>
+      </c>
+      <c r="C65" t="s">
         <v>81</v>
-      </c>
-      <c r="C65" t="s">
-        <v>82</v>
       </c>
       <c r="D65">
         <v>1690761600</v>
@@ -2279,13 +2293,13 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B66" t="s">
+        <v>80</v>
+      </c>
+      <c r="C66" t="s">
         <v>81</v>
-      </c>
-      <c r="C66" t="s">
-        <v>82</v>
       </c>
       <c r="D66">
         <v>1690761600</v>
@@ -2296,13 +2310,13 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B67" t="s">
+        <v>80</v>
+      </c>
+      <c r="C67" t="s">
         <v>81</v>
-      </c>
-      <c r="C67" t="s">
-        <v>82</v>
       </c>
       <c r="D67">
         <v>1690761600</v>
@@ -2313,13 +2327,13 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B68" t="s">
+        <v>80</v>
+      </c>
+      <c r="C68" t="s">
         <v>81</v>
-      </c>
-      <c r="C68" t="s">
-        <v>82</v>
       </c>
       <c r="D68">
         <v>1690761600</v>
@@ -2330,13 +2344,13 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
+        <v>91</v>
+      </c>
+      <c r="B69" t="s">
         <v>92</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
         <v>93</v>
-      </c>
-      <c r="C69" t="s">
-        <v>94</v>
       </c>
       <c r="D69">
         <v>1722384000</v>
@@ -2347,13 +2361,13 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B70" t="s">
+        <v>92</v>
+      </c>
+      <c r="C70" t="s">
         <v>93</v>
-      </c>
-      <c r="C70" t="s">
-        <v>94</v>
       </c>
       <c r="D70">
         <v>1722384000</v>
@@ -2364,13 +2378,13 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
+        <v>95</v>
+      </c>
+      <c r="B71" t="s">
         <v>96</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
         <v>97</v>
-      </c>
-      <c r="C71" t="s">
-        <v>98</v>
       </c>
       <c r="D71">
         <v>1722297600</v>
@@ -2381,13 +2395,13 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B72" t="s">
+        <v>96</v>
+      </c>
+      <c r="C72" t="s">
         <v>97</v>
-      </c>
-      <c r="C72" t="s">
-        <v>98</v>
       </c>
       <c r="D72">
         <v>1722297600</v>
@@ -2398,13 +2412,13 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B73" t="s">
+        <v>96</v>
+      </c>
+      <c r="C73" t="s">
         <v>97</v>
-      </c>
-      <c r="C73" t="s">
-        <v>98</v>
       </c>
       <c r="D73">
         <v>1722297600</v>
@@ -2415,13 +2429,13 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B74" t="s">
+        <v>96</v>
+      </c>
+      <c r="C74" t="s">
         <v>97</v>
-      </c>
-      <c r="C74" t="s">
-        <v>98</v>
       </c>
       <c r="D74">
         <v>1722297600</v>
@@ -2432,13 +2446,13 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B75" t="s">
+        <v>96</v>
+      </c>
+      <c r="C75" t="s">
         <v>97</v>
-      </c>
-      <c r="C75" t="s">
-        <v>98</v>
       </c>
       <c r="D75">
         <v>1722297600</v>
@@ -2449,13 +2463,13 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B76" t="s">
+        <v>96</v>
+      </c>
+      <c r="C76" t="s">
         <v>97</v>
-      </c>
-      <c r="C76" t="s">
-        <v>98</v>
       </c>
       <c r="D76">
         <v>1722297600</v>
@@ -2466,13 +2480,13 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
+        <v>103</v>
+      </c>
+      <c r="B77" t="s">
         <v>104</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" t="s">
         <v>105</v>
-      </c>
-      <c r="C77" t="s">
-        <v>106</v>
       </c>
       <c r="D77">
         <v>1785283200</v>
@@ -2483,13 +2497,13 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B78" t="s">
+        <v>104</v>
+      </c>
+      <c r="C78" t="s">
         <v>105</v>
-      </c>
-      <c r="C78" t="s">
-        <v>106</v>
       </c>
       <c r="D78">
         <v>1785283200</v>
@@ -2500,13 +2514,13 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B79" t="s">
+        <v>104</v>
+      </c>
+      <c r="C79" t="s">
         <v>105</v>
-      </c>
-      <c r="C79" t="s">
-        <v>106</v>
       </c>
       <c r="D79">
         <v>1785283200</v>
@@ -2517,13 +2531,13 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B80" t="s">
+        <v>104</v>
+      </c>
+      <c r="C80" t="s">
         <v>105</v>
-      </c>
-      <c r="C80" t="s">
-        <v>106</v>
       </c>
       <c r="D80">
         <v>1785283200</v>
@@ -2534,13 +2548,13 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B81" t="s">
+        <v>104</v>
+      </c>
+      <c r="C81" t="s">
         <v>105</v>
-      </c>
-      <c r="C81" t="s">
-        <v>106</v>
       </c>
       <c r="D81">
         <v>1785283200</v>
@@ -2551,13 +2565,13 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B82" t="s">
+        <v>104</v>
+      </c>
+      <c r="C82" t="s">
         <v>105</v>
-      </c>
-      <c r="C82" t="s">
-        <v>106</v>
       </c>
       <c r="D82">
         <v>1785283200</v>
@@ -2568,13 +2582,13 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B83" t="s">
+        <v>104</v>
+      </c>
+      <c r="C83" t="s">
         <v>105</v>
-      </c>
-      <c r="C83" t="s">
-        <v>106</v>
       </c>
       <c r="D83">
         <v>1785283200</v>
@@ -2585,13 +2599,13 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B84" t="s">
+        <v>104</v>
+      </c>
+      <c r="C84" t="s">
         <v>105</v>
-      </c>
-      <c r="C84" t="s">
-        <v>106</v>
       </c>
       <c r="D84">
         <v>1785283200</v>
@@ -2602,13 +2616,13 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
+        <v>113</v>
+      </c>
+      <c r="B85" t="s">
         <v>114</v>
       </c>
-      <c r="B85" t="s">
+      <c r="C85" t="s">
         <v>115</v>
-      </c>
-      <c r="C85" t="s">
-        <v>116</v>
       </c>
       <c r="D85">
         <v>1816732800</v>
@@ -2619,13 +2633,13 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B86" t="s">
+        <v>114</v>
+      </c>
+      <c r="C86" t="s">
         <v>115</v>
-      </c>
-      <c r="C86" t="s">
-        <v>116</v>
       </c>
       <c r="D86">
         <v>1816732800</v>
@@ -2636,13 +2650,13 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B87" t="s">
+        <v>114</v>
+      </c>
+      <c r="C87" t="s">
         <v>115</v>
-      </c>
-      <c r="C87" t="s">
-        <v>116</v>
       </c>
       <c r="D87">
         <v>1816732800</v>
@@ -2653,13 +2667,13 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B88" t="s">
+        <v>114</v>
+      </c>
+      <c r="C88" t="s">
         <v>115</v>
-      </c>
-      <c r="C88" t="s">
-        <v>116</v>
       </c>
       <c r="D88">
         <v>1816732800</v>
@@ -2670,13 +2684,13 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B89" t="s">
+        <v>114</v>
+      </c>
+      <c r="C89" t="s">
         <v>115</v>
-      </c>
-      <c r="C89" t="s">
-        <v>116</v>
       </c>
       <c r="D89">
         <v>1816732800</v>
@@ -2687,13 +2701,13 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B90" t="s">
+        <v>114</v>
+      </c>
+      <c r="C90" t="s">
         <v>115</v>
-      </c>
-      <c r="C90" t="s">
-        <v>116</v>
       </c>
       <c r="D90">
         <v>1816732800</v>
@@ -2704,13 +2718,13 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B91" t="s">
+        <v>114</v>
+      </c>
+      <c r="C91" t="s">
         <v>115</v>
-      </c>
-      <c r="C91" t="s">
-        <v>116</v>
       </c>
       <c r="D91">
         <v>1816732800</v>
@@ -2721,13 +2735,13 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B92" t="s">
+        <v>114</v>
+      </c>
+      <c r="C92" t="s">
         <v>115</v>
-      </c>
-      <c r="C92" t="s">
-        <v>116</v>
       </c>
       <c r="D92">
         <v>1816732800</v>
@@ -2738,13 +2752,13 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
+        <v>123</v>
+      </c>
+      <c r="B93" t="s">
         <v>124</v>
       </c>
-      <c r="B93" t="s">
+      <c r="C93" t="s">
         <v>125</v>
-      </c>
-      <c r="C93" t="s">
-        <v>126</v>
       </c>
       <c r="D93">
         <v>1849392000</v>
@@ -2755,13 +2769,13 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B94" t="s">
+        <v>124</v>
+      </c>
+      <c r="C94" t="s">
         <v>125</v>
-      </c>
-      <c r="C94" t="s">
-        <v>126</v>
       </c>
       <c r="D94">
         <v>1849392000</v>
@@ -2772,13 +2786,13 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B95" t="s">
+        <v>124</v>
+      </c>
+      <c r="C95" t="s">
         <v>125</v>
-      </c>
-      <c r="C95" t="s">
-        <v>126</v>
       </c>
       <c r="D95">
         <v>1849392000</v>
@@ -2789,13 +2803,13 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B96" t="s">
+        <v>124</v>
+      </c>
+      <c r="C96" t="s">
         <v>125</v>
-      </c>
-      <c r="C96" t="s">
-        <v>126</v>
       </c>
       <c r="D96">
         <v>1849392000</v>
@@ -2806,13 +2820,13 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
+        <v>129</v>
+      </c>
+      <c r="B97" t="s">
         <v>130</v>
       </c>
-      <c r="B97" t="s">
+      <c r="C97" t="s">
         <v>131</v>
-      </c>
-      <c r="C97" t="s">
-        <v>132</v>
       </c>
       <c r="E97" t="b">
         <v>1</v>
@@ -2823,13 +2837,13 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
+        <v>132</v>
+      </c>
+      <c r="B98" t="s">
         <v>133</v>
       </c>
-      <c r="B98" t="s">
-        <v>134</v>
-      </c>
       <c r="C98" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E98" t="b">
         <v>1</v>
@@ -2840,13 +2854,13 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
+        <v>134</v>
+      </c>
+      <c r="B99" t="s">
         <v>135</v>
       </c>
-      <c r="B99" t="s">
-        <v>136</v>
-      </c>
       <c r="C99" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E99" t="b">
         <v>1</v>
@@ -2857,13 +2871,13 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
+        <v>136</v>
+      </c>
+      <c r="B100" t="s">
         <v>137</v>
       </c>
-      <c r="B100" t="s">
-        <v>138</v>
-      </c>
       <c r="C100" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E100" t="b">
         <v>1</v>
@@ -2874,13 +2888,13 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
+        <v>138</v>
+      </c>
+      <c r="B101" t="s">
         <v>139</v>
       </c>
-      <c r="B101" t="s">
-        <v>140</v>
-      </c>
       <c r="C101" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E101" t="b">
         <v>1</v>
@@ -2891,13 +2905,13 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
+        <v>140</v>
+      </c>
+      <c r="B102" t="s">
         <v>141</v>
       </c>
-      <c r="B102" t="s">
+      <c r="C102" t="s">
         <v>142</v>
-      </c>
-      <c r="C102" t="s">
-        <v>143</v>
       </c>
       <c r="E102" t="b">
         <v>1</v>
@@ -2908,13 +2922,13 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
+        <v>143</v>
+      </c>
+      <c r="B103" t="s">
         <v>144</v>
       </c>
-      <c r="B103" t="s">
+      <c r="C103" t="s">
         <v>145</v>
-      </c>
-      <c r="C103" t="s">
-        <v>146</v>
       </c>
       <c r="E103" t="b">
         <v>1</v>
@@ -2925,13 +2939,13 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
+        <v>146</v>
+      </c>
+      <c r="B104" t="s">
         <v>147</v>
       </c>
-      <c r="B104" t="s">
-        <v>148</v>
-      </c>
       <c r="C104" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E104" t="b">
         <v>1</v>
@@ -2942,13 +2956,13 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
+        <v>148</v>
+      </c>
+      <c r="B105" t="s">
         <v>149</v>
       </c>
-      <c r="B105" t="s">
+      <c r="C105" t="s">
         <v>150</v>
-      </c>
-      <c r="C105" t="s">
-        <v>151</v>
       </c>
       <c r="E105" t="b">
         <v>1</v>
@@ -2959,13 +2973,13 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
+        <v>151</v>
+      </c>
+      <c r="B106" t="s">
         <v>152</v>
       </c>
-      <c r="B106" t="s">
+      <c r="C106" t="s">
         <v>153</v>
-      </c>
-      <c r="C106" t="s">
-        <v>154</v>
       </c>
       <c r="E106" t="b">
         <v>1</v>
@@ -2976,13 +2990,13 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
+        <v>154</v>
+      </c>
+      <c r="B107" t="s">
         <v>155</v>
       </c>
-      <c r="B107" t="s">
+      <c r="C107" t="s">
         <v>156</v>
-      </c>
-      <c r="C107" t="s">
-        <v>157</v>
       </c>
       <c r="E107" t="b">
         <v>1</v>
@@ -2993,13 +3007,13 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
+        <v>157</v>
+      </c>
+      <c r="B108" t="s">
         <v>158</v>
       </c>
-      <c r="B108" t="s">
-        <v>159</v>
-      </c>
       <c r="C108" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E108" t="b">
         <v>1</v>
@@ -3010,13 +3024,13 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
+        <v>159</v>
+      </c>
+      <c r="B109" t="s">
         <v>160</v>
       </c>
-      <c r="B109" t="s">
-        <v>161</v>
-      </c>
       <c r="C109" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E109" t="b">
         <v>1</v>
@@ -3027,13 +3041,13 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
+        <v>161</v>
+      </c>
+      <c r="B110" t="s">
         <v>162</v>
       </c>
-      <c r="B110" t="s">
+      <c r="C110" t="s">
         <v>163</v>
-      </c>
-      <c r="C110" t="s">
-        <v>164</v>
       </c>
       <c r="E110" t="b">
         <v>1</v>
@@ -3044,13 +3058,13 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
+        <v>164</v>
+      </c>
+      <c r="B111" t="s">
         <v>165</v>
       </c>
-      <c r="B111" t="s">
-        <v>166</v>
-      </c>
       <c r="C111" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D111">
         <v>1661731200</v>
@@ -3061,13 +3075,13 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
+        <v>166</v>
+      </c>
+      <c r="B112" t="s">
         <v>167</v>
       </c>
-      <c r="B112" t="s">
-        <v>168</v>
-      </c>
       <c r="C112" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D112">
         <v>1756598400</v>
@@ -3075,13 +3089,13 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B113" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C113" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D113">
         <v>1756598400</v>
@@ -3089,13 +3103,13 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
+        <v>169</v>
+      </c>
+      <c r="B114" t="s">
         <v>170</v>
       </c>
-      <c r="B114" t="s">
-        <v>171</v>
-      </c>
       <c r="C114" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D114">
         <v>1803772800</v>
@@ -3103,13 +3117,13 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B115" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C115" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D115">
         <v>1803772800</v>
@@ -3117,13 +3131,13 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B116" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C116" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D116">
         <v>1803772800</v>
@@ -3131,13 +3145,13 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
+        <v>173</v>
+      </c>
+      <c r="B117" t="s">
         <v>174</v>
       </c>
-      <c r="B117" t="s">
-        <v>175</v>
-      </c>
       <c r="C117" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D117">
         <v>1551398400</v>
@@ -3148,13 +3162,13 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
+        <v>175</v>
+      </c>
+      <c r="B118" t="s">
         <v>176</v>
       </c>
-      <c r="B118" t="s">
-        <v>177</v>
-      </c>
       <c r="C118" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D118">
         <v>1719705600</v>
@@ -3162,13 +3176,13 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
+        <v>177</v>
+      </c>
+      <c r="B119" t="s">
         <v>178</v>
       </c>
-      <c r="B119" t="s">
+      <c r="C119" t="s">
         <v>179</v>
-      </c>
-      <c r="C119" t="s">
-        <v>180</v>
       </c>
       <c r="D119">
         <v>1665360000</v>
@@ -3179,13 +3193,13 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B120" t="s">
+        <v>178</v>
+      </c>
+      <c r="C120" t="s">
         <v>179</v>
-      </c>
-      <c r="C120" t="s">
-        <v>180</v>
       </c>
       <c r="D120">
         <v>1665360000</v>
@@ -3196,24 +3210,24 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B121" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C121" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B122" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C122" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D122">
         <v>1857513600</v>
@@ -3224,13 +3238,13 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B123" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C123" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D123">
         <v>1538265600</v>
@@ -3238,13 +3252,13 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
+        <v>186</v>
+      </c>
+      <c r="B124" t="s">
+        <v>187</v>
+      </c>
+      <c r="C124" t="s">
         <v>188</v>
-      </c>
-      <c r="B124" t="s">
-        <v>189</v>
-      </c>
-      <c r="C124" t="s">
-        <v>190</v>
       </c>
       <c r="D124">
         <v>1528156800</v>
@@ -3255,13 +3269,13 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
+        <v>189</v>
+      </c>
+      <c r="B125" t="s">
+        <v>190</v>
+      </c>
+      <c r="C125" t="s">
         <v>191</v>
-      </c>
-      <c r="B125" t="s">
-        <v>192</v>
-      </c>
-      <c r="C125" t="s">
-        <v>193</v>
       </c>
       <c r="D125">
         <v>1616889600</v>
@@ -3272,13 +3286,13 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B126" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C126" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D126">
         <v>1640908800</v>
@@ -3289,13 +3303,13 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
+        <v>194</v>
+      </c>
+      <c r="B127" t="s">
+        <v>195</v>
+      </c>
+      <c r="C127" t="s">
         <v>196</v>
-      </c>
-      <c r="B127" t="s">
-        <v>197</v>
-      </c>
-      <c r="C127" t="s">
-        <v>198</v>
       </c>
       <c r="D127">
         <v>1849392000</v>
@@ -3303,13 +3317,13 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B128" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C128" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D128">
         <v>1553990400</v>
@@ -3317,35 +3331,35 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
+        <v>199</v>
+      </c>
+      <c r="B129" t="s">
+        <v>200</v>
+      </c>
+      <c r="C129" t="s">
         <v>201</v>
-      </c>
-      <c r="B129" t="s">
-        <v>202</v>
-      </c>
-      <c r="C129" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B130" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C130" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B131" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C131" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D131">
         <v>1972146600</v>
@@ -3356,24 +3370,24 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B132" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C132" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B133" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C133" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D133">
         <v>1756252800</v>
@@ -3381,13 +3395,13 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B134" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C134" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D134">
         <v>1809302400</v>
@@ -3395,13 +3409,13 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B135" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C135" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D135">
         <v>1809302400</v>
@@ -3409,13 +3423,13 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B136" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C136" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D136">
         <v>1809302400</v>
@@ -3423,13 +3437,13 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B137" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C137" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D137">
         <v>1809302400</v>
@@ -3437,13 +3451,13 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B138" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C138" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D138">
         <v>1809216000</v>
@@ -3451,13 +3465,13 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B139" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C139" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D139">
         <v>1809216000</v>
@@ -3465,13 +3479,13 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
+        <v>217</v>
+      </c>
+      <c r="B140" t="s">
+        <v>218</v>
+      </c>
+      <c r="C140" t="s">
         <v>219</v>
-      </c>
-      <c r="B140" t="s">
-        <v>220</v>
-      </c>
-      <c r="C140" t="s">
-        <v>221</v>
       </c>
       <c r="D140">
         <v>1809216000</v>
@@ -3479,24 +3493,24 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B141" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C141" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
+        <v>221</v>
+      </c>
+      <c r="B142" t="s">
+        <v>222</v>
+      </c>
+      <c r="C142" t="s">
         <v>223</v>
-      </c>
-      <c r="B142" t="s">
-        <v>224</v>
-      </c>
-      <c r="C142" t="s">
-        <v>225</v>
       </c>
       <c r="D142">
         <v>2064182400</v>
@@ -3507,13 +3521,13 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
+        <v>224</v>
+      </c>
+      <c r="B143" t="s">
+        <v>225</v>
+      </c>
+      <c r="C143" t="s">
         <v>226</v>
-      </c>
-      <c r="B143" t="s">
-        <v>227</v>
-      </c>
-      <c r="C143" t="s">
-        <v>228</v>
       </c>
       <c r="D143">
         <v>1719705600</v>
@@ -3524,13 +3538,13 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B144" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C144" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D144">
         <v>1785954600</v>
@@ -3544,13 +3558,13 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B145" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C145" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D145">
         <v>1719705600</v>
@@ -3561,13 +3575,13 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
+        <v>229</v>
+      </c>
+      <c r="B146" t="s">
+        <v>230</v>
+      </c>
+      <c r="C146" t="s">
         <v>231</v>
-      </c>
-      <c r="B146" t="s">
-        <v>232</v>
-      </c>
-      <c r="C146" t="s">
-        <v>233</v>
       </c>
       <c r="D146">
         <v>1874880000</v>
@@ -3578,13 +3592,13 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
+        <v>232</v>
+      </c>
+      <c r="B147" t="s">
+        <v>233</v>
+      </c>
+      <c r="C147" t="s">
         <v>234</v>
-      </c>
-      <c r="B147" t="s">
-        <v>235</v>
-      </c>
-      <c r="C147" t="s">
-        <v>236</v>
       </c>
       <c r="D147">
         <v>1969574400</v>
@@ -3595,13 +3609,13 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B148" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C148" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D148">
         <v>1969574400</v>
@@ -3612,13 +3626,13 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B149" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C149" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D149">
         <v>1969574400</v>
@@ -3629,13 +3643,13 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B150" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C150" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D150">
         <v>1969574400</v>
@@ -3646,13 +3660,13 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B151" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C151" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D151">
         <v>1874880000</v>
@@ -3663,13 +3677,13 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B152" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C152" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D152">
         <v>1969574400</v>
@@ -3680,13 +3694,13 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B153" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C153" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D153">
         <v>1969574400</v>
@@ -3697,13 +3711,13 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B154" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C154" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D154">
         <v>2064182400</v>
@@ -3714,13 +3728,13 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B155" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C155" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D155">
         <v>2064182400</v>
@@ -3731,13 +3745,13 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B156" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C156" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D156">
         <v>1969574400</v>
@@ -3748,13 +3762,13 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B157" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C157" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D157">
         <v>1969574400</v>
@@ -3765,13 +3779,13 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B158" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C158" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D158">
         <v>1969574400</v>
@@ -3782,13 +3796,13 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B159" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C159" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D159">
         <v>2064182400</v>
@@ -3799,35 +3813,35 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B160" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C160" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B161" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C161" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
+        <v>252</v>
+      </c>
+      <c r="B162" t="s">
+        <v>253</v>
+      </c>
+      <c r="C162" t="s">
         <v>254</v>
-      </c>
-      <c r="B162" t="s">
-        <v>255</v>
-      </c>
-      <c r="C162" t="s">
-        <v>256</v>
       </c>
       <c r="D162">
         <v>1293753600</v>
@@ -3838,24 +3852,24 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B163" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C163" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
+        <v>256</v>
+      </c>
+      <c r="B164" t="s">
+        <v>257</v>
+      </c>
+      <c r="C164" t="s">
         <v>258</v>
-      </c>
-      <c r="B164" t="s">
-        <v>259</v>
-      </c>
-      <c r="C164" t="s">
-        <v>260</v>
       </c>
       <c r="D164">
         <v>1806537600</v>
@@ -3866,13 +3880,13 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
+        <v>259</v>
+      </c>
+      <c r="B165" t="s">
+        <v>260</v>
+      </c>
+      <c r="C165" t="s">
         <v>261</v>
-      </c>
-      <c r="B165" t="s">
-        <v>262</v>
-      </c>
-      <c r="C165" t="s">
-        <v>263</v>
       </c>
       <c r="D165">
         <v>1874880000</v>
@@ -3883,24 +3897,24 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B166" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C166" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B167" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C167" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D167">
         <v>1849651200</v>
@@ -3908,13 +3922,13 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
+        <v>266</v>
+      </c>
+      <c r="B168" t="s">
+        <v>267</v>
+      </c>
+      <c r="C168" t="s">
         <v>268</v>
-      </c>
-      <c r="B168" t="s">
-        <v>269</v>
-      </c>
-      <c r="C168" t="s">
-        <v>270</v>
       </c>
       <c r="D168">
         <v>1799712000</v>
@@ -3925,13 +3939,13 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B169" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C169" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D169">
         <v>1799712000</v>
@@ -3942,13 +3956,13 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B170" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C170" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D170">
         <v>1799712000</v>
@@ -3959,13 +3973,13 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
+        <v>271</v>
+      </c>
+      <c r="B171" t="s">
+        <v>272</v>
+      </c>
+      <c r="C171" t="s">
         <v>273</v>
-      </c>
-      <c r="B171" t="s">
-        <v>274</v>
-      </c>
-      <c r="C171" t="s">
-        <v>275</v>
       </c>
       <c r="D171">
         <v>1862611200</v>
@@ -3976,13 +3990,13 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B172" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C172" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D172">
         <v>1862611200</v>
@@ -3993,13 +4007,13 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
+        <v>275</v>
+      </c>
+      <c r="B173" t="s">
+        <v>276</v>
+      </c>
+      <c r="C173" t="s">
         <v>277</v>
-      </c>
-      <c r="B173" t="s">
-        <v>278</v>
-      </c>
-      <c r="C173" t="s">
-        <v>279</v>
       </c>
       <c r="D173">
         <v>1949702400</v>
@@ -4010,13 +4024,13 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B174" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C174" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D174">
         <v>1949702400</v>
@@ -4027,13 +4041,13 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
+        <v>279</v>
+      </c>
+      <c r="B175" t="s">
+        <v>280</v>
+      </c>
+      <c r="C175" t="s">
         <v>281</v>
-      </c>
-      <c r="B175" t="s">
-        <v>282</v>
-      </c>
-      <c r="C175" t="s">
-        <v>283</v>
       </c>
       <c r="D175">
         <v>2047075200</v>
